--- a/data_input/typology_class_combo_emissions.xlsx
+++ b/data_input/typology_class_combo_emissions.xlsx
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6377.921629210594</v>
+        <v>5489.877702063777</v>
       </c>
       <c r="D2" t="n">
-        <v>5306.276426189853</v>
+        <v>4428.303923288431</v>
       </c>
       <c r="E2" t="n">
-        <v>5828.962448591719</v>
+        <v>4646.171981168795</v>
       </c>
       <c r="F2" t="n">
-        <v>5842.974304957693</v>
+        <v>4892.261961081991</v>
       </c>
       <c r="G2" t="n">
-        <v>2345810</v>
+        <v>2435385</v>
       </c>
     </row>
     <row r="3">
@@ -504,19 +504,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10987.49189854286</v>
+        <v>9377.689862340778</v>
       </c>
       <c r="D3" t="n">
-        <v>7658.941041718369</v>
+        <v>6706.930190072303</v>
       </c>
       <c r="E3" t="n">
-        <v>8770.579914911623</v>
+        <v>7022.35421696803</v>
       </c>
       <c r="F3" t="n">
-        <v>9313.60518443836</v>
+        <v>7638.258589970857</v>
       </c>
       <c r="G3" t="n">
-        <v>112665</v>
+        <v>107480</v>
       </c>
     </row>
     <row r="4">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7523.491433603667</v>
+        <v>6263.467842375323</v>
       </c>
       <c r="D4" t="n">
-        <v>5450.814615610396</v>
+        <v>4798.163975956058</v>
       </c>
       <c r="E4" t="n">
-        <v>6561.570523684385</v>
+        <v>5902.336447116666</v>
       </c>
       <c r="F4" t="n">
-        <v>6467.755909793927</v>
+        <v>5613.842849741312</v>
       </c>
       <c r="G4" t="n">
-        <v>5660</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="5">
@@ -558,19 +558,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7149.382960972376</v>
+        <v>6856.560316007463</v>
       </c>
       <c r="D5" t="n">
-        <v>4820.771990037463</v>
+        <v>4468.895865610992</v>
       </c>
       <c r="E5" t="n">
-        <v>6424.390031906311</v>
+        <v>5811.008847314267</v>
       </c>
       <c r="F5" t="n">
-        <v>6311.836188053942</v>
+        <v>5721.385431421038</v>
       </c>
       <c r="G5" t="n">
-        <v>1192140</v>
+        <v>1214345</v>
       </c>
     </row>
     <row r="6">
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11944.58732442599</v>
+        <v>6544.393529997739</v>
       </c>
       <c r="D6" t="n">
-        <v>5238.971610431654</v>
+        <v>4237.505181626087</v>
       </c>
       <c r="E6" t="n">
-        <v>7133.277192901137</v>
+        <v>5735.381717538879</v>
       </c>
       <c r="F6" t="n">
-        <v>7591.547967414377</v>
+        <v>5706.17731486861</v>
       </c>
       <c r="G6" t="n">
-        <v>764615</v>
+        <v>943060</v>
       </c>
     </row>
     <row r="7">
@@ -612,19 +612,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6861.832087408879</v>
+        <v>5991.233202686336</v>
       </c>
       <c r="D7" t="n">
-        <v>3293.025163421462</v>
+        <v>3000.201665914263</v>
       </c>
       <c r="E7" t="n">
-        <v>4716.771949011476</v>
+        <v>4039.675989229487</v>
       </c>
       <c r="F7" t="n">
-        <v>4827.483108542388</v>
+        <v>4417.867329590699</v>
       </c>
       <c r="G7" t="n">
-        <v>1897120</v>
+        <v>1895525</v>
       </c>
     </row>
     <row r="8">
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5280.767692124763</v>
+        <v>4854.986454913957</v>
       </c>
       <c r="D8" t="n">
-        <v>3778.160582000226</v>
+        <v>3334.619606783634</v>
       </c>
       <c r="E8" t="n">
-        <v>4476.425445977616</v>
+        <v>3815.326299624254</v>
       </c>
       <c r="F8" t="n">
-        <v>4508.761168991484</v>
+        <v>4033.051000660745</v>
       </c>
       <c r="G8" t="n">
-        <v>3955720</v>
+        <v>3973910</v>
       </c>
     </row>
     <row r="9">
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8893.106943405837</v>
+        <v>4579.438194532134</v>
       </c>
       <c r="D9" t="n">
-        <v>4455.75129493658</v>
+        <v>3630.09418701205</v>
       </c>
       <c r="E9" t="n">
-        <v>4615.648081507752</v>
+        <v>4116.620398576352</v>
       </c>
       <c r="F9" t="n">
-        <v>5653.559189100072</v>
+        <v>4131.896411069427</v>
       </c>
       <c r="G9" t="n">
-        <v>253875</v>
+        <v>282160</v>
       </c>
     </row>
     <row r="10">
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4387.595644991877</v>
+        <v>3860.128216891741</v>
       </c>
       <c r="D10" t="n">
-        <v>2825.294882776402</v>
+        <v>2396.895055655953</v>
       </c>
       <c r="E10" t="n">
-        <v>3310.955528946273</v>
+        <v>2755.057301259241</v>
       </c>
       <c r="F10" t="n">
-        <v>3390.254611412484</v>
+        <v>3001.924983852329</v>
       </c>
       <c r="G10" t="n">
-        <v>1280595</v>
+        <v>1283580</v>
       </c>
     </row>
     <row r="11">
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5577.023303838034</v>
+        <v>4977.488790525601</v>
       </c>
       <c r="D11" t="n">
-        <v>4243.178754697525</v>
+        <v>3675.464159007716</v>
       </c>
       <c r="E11" t="n">
-        <v>4943.49417043611</v>
+        <v>4070.979075459233</v>
       </c>
       <c r="F11" t="n">
-        <v>4930.709542463652</v>
+        <v>4287.24346004364</v>
       </c>
       <c r="G11" t="n">
-        <v>3192685</v>
+        <v>3286410</v>
       </c>
     </row>
     <row r="12">
@@ -747,19 +747,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9490.445059358733</v>
+        <v>5448.115574969082</v>
       </c>
       <c r="D12" t="n">
-        <v>5273.848300187878</v>
+        <v>4350.128307305845</v>
       </c>
       <c r="E12" t="n">
-        <v>5618.63721107253</v>
+        <v>4794.614216689673</v>
       </c>
       <c r="F12" t="n">
-        <v>6443.286349010364</v>
+        <v>4868.053180336389</v>
       </c>
       <c r="G12" t="n">
-        <v>155535</v>
+        <v>159455</v>
       </c>
     </row>
     <row r="13">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4882.450233503636</v>
+        <v>4254.760218060303</v>
       </c>
       <c r="D13" t="n">
-        <v>3206.560618634934</v>
+        <v>2719.682303042932</v>
       </c>
       <c r="E13" t="n">
-        <v>3788.368017194821</v>
+        <v>3135.222149768143</v>
       </c>
       <c r="F13" t="n">
-        <v>3846.15243225543</v>
+        <v>3371.70624106163</v>
       </c>
       <c r="G13" t="n">
-        <v>659440</v>
+        <v>653305</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/typology_class_combo_emissions.xlsx
+++ b/data_input/typology_class_combo_emissions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>tenure_lab</t>
+          <t>inc_lab</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -473,23 +473,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5489.877702063777</v>
+        <v>4985.743576559914</v>
       </c>
       <c r="D2" t="n">
-        <v>4428.303923288431</v>
+        <v>3742.633389894152</v>
       </c>
       <c r="E2" t="n">
-        <v>4646.171981168795</v>
+        <v>4302.608746086029</v>
       </c>
       <c r="F2" t="n">
-        <v>4892.261961081991</v>
+        <v>4415.064754944737</v>
       </c>
       <c r="G2" t="n">
-        <v>2435385</v>
+        <v>1308040</v>
       </c>
     </row>
     <row r="3">
@@ -500,23 +500,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>priate rental</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9377.689862340778</v>
+        <v>5954.567676114597</v>
       </c>
       <c r="D3" t="n">
-        <v>6706.930190072303</v>
+        <v>4618.428265112355</v>
       </c>
       <c r="E3" t="n">
-        <v>7022.35421696803</v>
+        <v>5117.834120730186</v>
       </c>
       <c r="F3" t="n">
-        <v>7638.258589970857</v>
+        <v>5266.05810204621</v>
       </c>
       <c r="G3" t="n">
-        <v>107480</v>
+        <v>543240</v>
       </c>
     </row>
     <row r="4">
@@ -527,50 +527,50 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>poorest 50%</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6263.467842375323</v>
+        <v>5003.052273662324</v>
       </c>
       <c r="D4" t="n">
-        <v>4798.163975956058</v>
+        <v>3730.869870779442</v>
       </c>
       <c r="E4" t="n">
-        <v>5902.336447116666</v>
+        <v>4084.627978963247</v>
       </c>
       <c r="F4" t="n">
-        <v>5613.842849741312</v>
+        <v>4245.355276031803</v>
       </c>
       <c r="G4" t="n">
-        <v>5240</v>
+        <v>607300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>detached</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>top 1%</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6856.560316007463</v>
+        <v>8957.721666154381</v>
       </c>
       <c r="D5" t="n">
-        <v>4468.895865610992</v>
+        <v>5418.557822879374</v>
       </c>
       <c r="E5" t="n">
-        <v>5811.008847314267</v>
+        <v>6548.976388886523</v>
       </c>
       <c r="F5" t="n">
-        <v>5721.385431421038</v>
+        <v>6863.198486005007</v>
       </c>
       <c r="G5" t="n">
-        <v>1214345</v>
+        <v>90465</v>
       </c>
     </row>
     <row r="6">
@@ -581,23 +581,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>priate rental</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6544.393529997739</v>
+        <v>6478.397137832225</v>
       </c>
       <c r="D6" t="n">
-        <v>4237.505181626087</v>
+        <v>3631.786219579132</v>
       </c>
       <c r="E6" t="n">
-        <v>5735.381717538879</v>
+        <v>5012.11485654138</v>
       </c>
       <c r="F6" t="n">
-        <v>5706.17731486861</v>
+        <v>5070.704665844371</v>
       </c>
       <c r="G6" t="n">
-        <v>943060</v>
+        <v>1203210</v>
       </c>
     </row>
     <row r="7">
@@ -608,77 +608,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5991.233202686336</v>
+        <v>6985.978957389824</v>
       </c>
       <c r="D7" t="n">
-        <v>3000.201665914263</v>
+        <v>4449.235585862238</v>
       </c>
       <c r="E7" t="n">
-        <v>4039.675989229487</v>
+        <v>6007.608793897572</v>
       </c>
       <c r="F7" t="n">
-        <v>4417.867329590699</v>
+        <v>5911.999338110349</v>
       </c>
       <c r="G7" t="n">
-        <v>1895525</v>
+        <v>257735</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>row house</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>poorest 50%</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4854.986454913957</v>
+        <v>5596.44071680236</v>
       </c>
       <c r="D8" t="n">
-        <v>3334.619606783634</v>
+        <v>2906.882403903905</v>
       </c>
       <c r="E8" t="n">
-        <v>3815.326299624254</v>
+        <v>4147.878472864532</v>
       </c>
       <c r="F8" t="n">
-        <v>4033.051000660745</v>
+        <v>4248.819468770578</v>
       </c>
       <c r="G8" t="n">
-        <v>3973910</v>
+        <v>2566755</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>row house</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>priate rental</t>
+          <t>top 1%</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4579.438194532134</v>
+        <v>10641.42374291252</v>
       </c>
       <c r="D9" t="n">
-        <v>3630.09418701205</v>
+        <v>5891.795033361172</v>
       </c>
       <c r="E9" t="n">
-        <v>4116.620398576352</v>
+        <v>7026.793271755811</v>
       </c>
       <c r="F9" t="n">
-        <v>4131.896411069427</v>
+        <v>7485.021284676914</v>
       </c>
       <c r="G9" t="n">
-        <v>282160</v>
+        <v>29710</v>
       </c>
     </row>
     <row r="10">
@@ -689,104 +689,212 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3860.128216891741</v>
+        <v>4515.5740240542</v>
       </c>
       <c r="D10" t="n">
-        <v>2396.895055655953</v>
+        <v>2848.904155705424</v>
       </c>
       <c r="E10" t="n">
-        <v>2755.057301259241</v>
+        <v>3606.039305736101</v>
       </c>
       <c r="F10" t="n">
-        <v>3001.924983852329</v>
+        <v>3778.874000430048</v>
       </c>
       <c r="G10" t="n">
-        <v>1283580</v>
+        <v>2676820</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>semi-detached</t>
+          <t>row house</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4977.488790525601</v>
+        <v>5834.458444706745</v>
       </c>
       <c r="D11" t="n">
-        <v>3675.464159007716</v>
+        <v>3616.504143300569</v>
       </c>
       <c r="E11" t="n">
-        <v>4070.979075459233</v>
+        <v>4606.05448554169</v>
       </c>
       <c r="F11" t="n">
-        <v>4287.24346004364</v>
+        <v>4707.418929444269</v>
       </c>
       <c r="G11" t="n">
-        <v>3286410</v>
+        <v>490575</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>semi-detached</t>
+          <t>row house</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>priate rental</t>
+          <t>poorest 50%</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5448.115574969082</v>
+        <v>4154.099087841259</v>
       </c>
       <c r="D12" t="n">
-        <v>4350.128307305845</v>
+        <v>2455.158334517435</v>
       </c>
       <c r="E12" t="n">
-        <v>4794.614216689673</v>
+        <v>2930.664823023083</v>
       </c>
       <c r="F12" t="n">
-        <v>4868.053180336389</v>
+        <v>3123.007976514416</v>
       </c>
       <c r="G12" t="n">
-        <v>159455</v>
+        <v>2342555</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>top 1%</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8248.5577978526</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4855.010024182614</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5818.351726334409</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6227.517923766508</v>
+      </c>
+      <c r="G13" t="n">
+        <v>31110</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>semi-detached</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>social rental</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>4254.760218060303</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2719.682303042932</v>
-      </c>
-      <c r="E13" t="n">
-        <v>3135.222149768143</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3371.70624106163</v>
-      </c>
-      <c r="G13" t="n">
-        <v>653305</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>51-90%</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4597.391821955891</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3152.010211842918</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3790.518849217571</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3955.753663933195</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2078210</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>91-99%</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5752.025447409799</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3968.216240389798</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4774.09913849043</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4889.704127721014</v>
+      </c>
+      <c r="G15" t="n">
+        <v>460835</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>poorest 50%</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4461.629755477563</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2798.992850811739</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3332.766539539072</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3488.966322138053</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1523480</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>top 1%</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8124.520216181863</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4849.432684221696</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6000.145038559343</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6374.006871104274</v>
+      </c>
+      <c r="G17" t="n">
+        <v>37550</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/typology_class_combo_emissions.xlsx
+++ b/data_input/typology_class_combo_emissions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,23 +473,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51-90%</t>
+          <t>decile 1 (poorest)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4985.743576559914</v>
+        <v>5299.685652077666</v>
       </c>
       <c r="D2" t="n">
-        <v>3742.633389894152</v>
+        <v>3908.904393004301</v>
       </c>
       <c r="E2" t="n">
-        <v>4302.608746086029</v>
+        <v>4076.103939955301</v>
       </c>
       <c r="F2" t="n">
-        <v>4415.064754944737</v>
+        <v>4353.769496554987</v>
       </c>
       <c r="G2" t="n">
-        <v>1308040</v>
+        <v>75725</v>
       </c>
     </row>
     <row r="3">
@@ -500,23 +500,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91-99%</t>
+          <t>decile 10 (richest)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5954.567676114597</v>
+        <v>6044.486568191954</v>
       </c>
       <c r="D3" t="n">
-        <v>4618.428265112355</v>
+        <v>4896.879161977036</v>
       </c>
       <c r="E3" t="n">
-        <v>5117.834120730186</v>
+        <v>5303.059251865821</v>
       </c>
       <c r="F3" t="n">
-        <v>5266.05810204621</v>
+        <v>5436.241983383848</v>
       </c>
       <c r="G3" t="n">
-        <v>543240</v>
+        <v>633770</v>
       </c>
     </row>
     <row r="4">
@@ -527,23 +527,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>poorest 50%</t>
+          <t>decile 2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5003.052273662324</v>
+        <v>4478.973812094879</v>
       </c>
       <c r="D4" t="n">
-        <v>3730.869870779442</v>
+        <v>3751.54886416195</v>
       </c>
       <c r="E4" t="n">
-        <v>4084.627978963247</v>
+        <v>3894.817204797086</v>
       </c>
       <c r="F4" t="n">
-        <v>4245.355276031803</v>
+        <v>4071.81063107252</v>
       </c>
       <c r="G4" t="n">
-        <v>607300</v>
+        <v>64960</v>
       </c>
     </row>
     <row r="5">
@@ -554,347 +554,995 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>top 1%</t>
+          <t>decile 3</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8957.721666154381</v>
+        <v>4492.570083853862</v>
       </c>
       <c r="D5" t="n">
-        <v>5418.557822879374</v>
+        <v>3626.014990956859</v>
       </c>
       <c r="E5" t="n">
-        <v>6548.976388886523</v>
+        <v>4066.991989777974</v>
       </c>
       <c r="F5" t="n">
-        <v>6863.198486005007</v>
+        <v>4034.901455055867</v>
       </c>
       <c r="G5" t="n">
-        <v>90465</v>
+        <v>107475</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>detached</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51-90%</t>
+          <t>decile 4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6478.397137832225</v>
+        <v>4849.055693503766</v>
       </c>
       <c r="D6" t="n">
-        <v>3631.786219579132</v>
+        <v>3757.803361000632</v>
       </c>
       <c r="E6" t="n">
-        <v>5012.11485654138</v>
+        <v>4648.724333456104</v>
       </c>
       <c r="F6" t="n">
-        <v>5070.704665844371</v>
+        <v>4444.104371154798</v>
       </c>
       <c r="G6" t="n">
-        <v>1203210</v>
+        <v>160570</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>detached</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91-99%</t>
+          <t>decile 5</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6985.978957389824</v>
+        <v>5623.227367907934</v>
       </c>
       <c r="D7" t="n">
-        <v>4449.235585862238</v>
+        <v>3970.066989034565</v>
       </c>
       <c r="E7" t="n">
-        <v>6007.608793897572</v>
+        <v>4113.859139250159</v>
       </c>
       <c r="F7" t="n">
-        <v>5911.999338110349</v>
+        <v>4481.257971149733</v>
       </c>
       <c r="G7" t="n">
-        <v>257735</v>
+        <v>198105</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>detached</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>poorest 50%</t>
+          <t>decile 6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5596.44071680236</v>
+        <v>4950.402189674432</v>
       </c>
       <c r="D8" t="n">
-        <v>2906.882403903905</v>
+        <v>3460.790363030416</v>
       </c>
       <c r="E8" t="n">
-        <v>4147.878472864532</v>
+        <v>4130.256190144873</v>
       </c>
       <c r="F8" t="n">
-        <v>4248.819468770578</v>
+        <v>4151.608173933843</v>
       </c>
       <c r="G8" t="n">
-        <v>2566755</v>
+        <v>246495</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>detached</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>top 1%</t>
+          <t>decile 7</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10641.42374291252</v>
+        <v>4952.972604706457</v>
       </c>
       <c r="D9" t="n">
-        <v>5891.795033361172</v>
+        <v>3619.446603697561</v>
       </c>
       <c r="E9" t="n">
-        <v>7026.793271755811</v>
+        <v>4285.866315005616</v>
       </c>
       <c r="F9" t="n">
-        <v>7485.021284676914</v>
+        <v>4292.398461265519</v>
       </c>
       <c r="G9" t="n">
-        <v>29710</v>
+        <v>287895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>row house</t>
+          <t>detached</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>51-90%</t>
+          <t>decile 8</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4515.5740240542</v>
+        <v>5711.590216834343</v>
       </c>
       <c r="D10" t="n">
-        <v>2848.904155705424</v>
+        <v>3796.786644305857</v>
       </c>
       <c r="E10" t="n">
-        <v>3606.039305736101</v>
+        <v>4694.030383611409</v>
       </c>
       <c r="F10" t="n">
-        <v>3778.874000430048</v>
+        <v>4645.859706107588</v>
       </c>
       <c r="G10" t="n">
-        <v>2676820</v>
+        <v>348355</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>row house</t>
+          <t>detached</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>91-99%</t>
+          <t>decile 9</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5834.458444706745</v>
+        <v>5061.319693907812</v>
       </c>
       <c r="D11" t="n">
-        <v>3616.504143300569</v>
+        <v>4046.342001754093</v>
       </c>
       <c r="E11" t="n">
-        <v>4606.05448554169</v>
+        <v>4576.9135828685</v>
       </c>
       <c r="F11" t="n">
-        <v>4707.418929444269</v>
+        <v>4599.935816349162</v>
       </c>
       <c r="G11" t="n">
-        <v>490575</v>
+        <v>425130</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>row house</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>poorest 50%</t>
+          <t>decile 1 (poorest)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4154.099087841259</v>
+        <v>4984.850737288224</v>
       </c>
       <c r="D12" t="n">
-        <v>2455.158334517435</v>
+        <v>2340.045845033093</v>
       </c>
       <c r="E12" t="n">
-        <v>2930.664823023083</v>
+        <v>3266.873600760683</v>
       </c>
       <c r="F12" t="n">
-        <v>3123.007976514416</v>
+        <v>3524.792155709378</v>
       </c>
       <c r="G12" t="n">
-        <v>2342555</v>
+        <v>696670</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>row house</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>top 1%</t>
+          <t>decile 10 (richest)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8248.5577978526</v>
+        <v>6949.841478606488</v>
       </c>
       <c r="D13" t="n">
-        <v>4855.010024182614</v>
+        <v>4707.823492620956</v>
       </c>
       <c r="E13" t="n">
-        <v>5818.351726334409</v>
+        <v>6247.778002951329</v>
       </c>
       <c r="F13" t="n">
-        <v>6227.517923766508</v>
+        <v>6039.917685662316</v>
       </c>
       <c r="G13" t="n">
-        <v>31110</v>
+        <v>287865</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>semi-detached</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>51-90%</t>
+          <t>decile 2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4597.391821955891</v>
+        <v>4514.028403035381</v>
       </c>
       <c r="D14" t="n">
-        <v>3152.010211842918</v>
+        <v>2724.25328354728</v>
       </c>
       <c r="E14" t="n">
-        <v>3790.518849217571</v>
+        <v>3454.29714594401</v>
       </c>
       <c r="F14" t="n">
-        <v>3955.753663933195</v>
+        <v>3697.556101160057</v>
       </c>
       <c r="G14" t="n">
-        <v>2078210</v>
+        <v>565725</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>semi-detached</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>91-99%</t>
+          <t>decile 3</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5752.025447409799</v>
+        <v>4671.895739999127</v>
       </c>
       <c r="D15" t="n">
-        <v>3968.216240389798</v>
+        <v>2865.974561453333</v>
       </c>
       <c r="E15" t="n">
-        <v>4774.09913849043</v>
+        <v>3984.373020090701</v>
       </c>
       <c r="F15" t="n">
-        <v>4889.704127721014</v>
+        <v>3867.286649469769</v>
       </c>
       <c r="G15" t="n">
-        <v>460835</v>
+        <v>494365</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>semi-detached</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>poorest 50%</t>
+          <t>decile 4</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4461.629755477563</v>
+        <v>5363.639473101308</v>
       </c>
       <c r="D16" t="n">
-        <v>2798.992850811739</v>
+        <v>3150.772107210704</v>
       </c>
       <c r="E16" t="n">
-        <v>3332.766539539072</v>
+        <v>4920.498037600655</v>
       </c>
       <c r="F16" t="n">
-        <v>3488.966322138053</v>
+        <v>4510.84648171901</v>
       </c>
       <c r="G16" t="n">
-        <v>1523480</v>
+        <v>429550</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>decile 5</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6450.748969703031</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3591.857986758945</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4461.749876024409</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4883.739413786099</v>
+      </c>
+      <c r="G17" t="n">
+        <v>380425</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>decile 6</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5411.378954223218</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3230.50807182099</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4770.212727629429</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4604.616225958704</v>
+      </c>
+      <c r="G18" t="n">
+        <v>335225</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>decile 7</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6393.752832412273</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3516.658407323132</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4843.198408758136</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4882.517974675734</v>
+      </c>
+      <c r="G19" t="n">
+        <v>305820</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>decile 8</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>7471.834488895447</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3643.865238296513</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5210.923695237904</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5338.396888231678</v>
+      </c>
+      <c r="G20" t="n">
+        <v>287890</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>decile 9</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6296.808282985407</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4003.182684656293</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5057.111486514842</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5204.427549177861</v>
+      </c>
+      <c r="G21" t="n">
+        <v>274205</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>decile 1 (poorest)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3460.734326983153</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2101.120858799821</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2334.51534600951</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2579.693841249952</v>
+      </c>
+      <c r="G22" t="n">
+        <v>391135</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>decile 10 (richest)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5841.020028160136</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3860.202402977864</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4661.161182050686</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4803.898538339394</v>
+      </c>
+      <c r="G23" t="n">
+        <v>521965</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>decile 2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3521.974924191022</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2407.381367641814</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2708.586906054574</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2951.086388379988</v>
+      </c>
+      <c r="G24" t="n">
+        <v>392680</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>decile 3</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3568.875854252115</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2437.123005159699</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2977.546571877547</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2942.221421694903</v>
+      </c>
+      <c r="G25" t="n">
+        <v>424500</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>decile 4</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3920.049801459709</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2658.307227391697</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3343.469276299834</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3272.217729496656</v>
+      </c>
+      <c r="G26" t="n">
+        <v>528290</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>decile 5</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5061.699694363081</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2728.530599995424</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3001.445312173605</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3485.694809158601</v>
+      </c>
+      <c r="G27" t="n">
+        <v>605905</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>decile 6</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4527.522688995416</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2534.800120772333</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3180.911371072953</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3344.978343923123</v>
+      </c>
+      <c r="G28" t="n">
+        <v>659110</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>decile 7</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4427.64720888718</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2749.128574791855</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3492.902171789032</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3587.816689164998</v>
+      </c>
+      <c r="G29" t="n">
+        <v>675165</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>decile 8</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5338.86523336984</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2873.11349614364</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3909.123715996295</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4060.333816448479</v>
+      </c>
+      <c r="G30" t="n">
+        <v>682730</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>decile 9</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4798.384414874695</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3186.675254862184</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4052.841171685796</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4060.266197488509</v>
+      </c>
+      <c r="G31" t="n">
+        <v>659770</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>semi-detached</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>top 1%</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>8124.520216181863</v>
-      </c>
-      <c r="D17" t="n">
-        <v>4849.432684221696</v>
-      </c>
-      <c r="E17" t="n">
-        <v>6000.145038559343</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6374.006871104274</v>
-      </c>
-      <c r="G17" t="n">
-        <v>37550</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>decile 1 (poorest)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4062.159297121251</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2424.545453717012</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2763.618906322488</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3030.214338368642</v>
+      </c>
+      <c r="G32" t="n">
+        <v>216185</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>decile 10 (richest)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5803.112968791757</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4220.49870381027</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4848.937961188008</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5001.317065163477</v>
+      </c>
+      <c r="G33" t="n">
+        <v>498420</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>decile 2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3907.66985185382</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2759.458690390209</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3141.255787812888</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3342.608631318451</v>
+      </c>
+      <c r="G34" t="n">
+        <v>241005</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>decile 3</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3929.406887807512</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2797.467537827977</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3408.456177340279</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3348.906681279869</v>
+      </c>
+      <c r="G35" t="n">
+        <v>277775</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>decile 4</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4280.872634773366</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3008.035752203092</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3786.451902208779</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3671.49497087552</v>
+      </c>
+      <c r="G36" t="n">
+        <v>361795</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>decile 5</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5148.226516206169</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3087.925888286128</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3322.568473833757</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3765.318469463719</v>
+      </c>
+      <c r="G37" t="n">
+        <v>426550</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>decile 6</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4551.796427748211</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2849.282139105831</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3451.400967036993</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3571.087235489444</v>
+      </c>
+      <c r="G38" t="n">
+        <v>483050</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>decile 7</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4474.805643292028</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3045.28776304309</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3663.297556838647</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3766.612230398041</v>
+      </c>
+      <c r="G39" t="n">
+        <v>514690</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>decile 8</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>5330.366694522197</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3166.963371276879</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4133.44622952016</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4193.724631296665</v>
+      </c>
+      <c r="G40" t="n">
+        <v>535815</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>decile 9</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4804.031089229067</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3493.168214288798</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4203.272754992187</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4229.490387113944</v>
+      </c>
+      <c r="G41" t="n">
+        <v>544675</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/typology_class_combo_emissions.xlsx
+++ b/data_input/typology_class_combo_emissions.xlsx
@@ -477,16 +477,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5489.877702063777</v>
+        <v>5581.095721343929</v>
       </c>
       <c r="D2" t="n">
-        <v>4428.303923288431</v>
+        <v>4694.689418447797</v>
       </c>
       <c r="E2" t="n">
-        <v>4646.171981168795</v>
+        <v>4825.426378082513</v>
       </c>
       <c r="F2" t="n">
-        <v>4892.261961081991</v>
+        <v>5055.878985103967</v>
       </c>
       <c r="G2" t="n">
         <v>2435385</v>
@@ -504,16 +504,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9377.689862340778</v>
+        <v>9016.349284731297</v>
       </c>
       <c r="D3" t="n">
-        <v>6706.930190072303</v>
+        <v>6958.997753521457</v>
       </c>
       <c r="E3" t="n">
-        <v>7022.35421696803</v>
+        <v>7091.124522305787</v>
       </c>
       <c r="F3" t="n">
-        <v>7638.258589970857</v>
+        <v>7646.991750279551</v>
       </c>
       <c r="G3" t="n">
         <v>107480</v>
@@ -531,16 +531,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6263.467842375323</v>
+        <v>6169.284248133609</v>
       </c>
       <c r="D4" t="n">
-        <v>4798.163975956058</v>
+        <v>4733.062415568348</v>
       </c>
       <c r="E4" t="n">
-        <v>5902.336447116666</v>
+        <v>5589.101621420755</v>
       </c>
       <c r="F4" t="n">
-        <v>5613.842849741312</v>
+        <v>5556.859111992361</v>
       </c>
       <c r="G4" t="n">
         <v>5240</v>
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6856.560316007463</v>
+        <v>5740.136885743651</v>
       </c>
       <c r="D5" t="n">
-        <v>4468.895865610992</v>
+        <v>4121.144441110479</v>
       </c>
       <c r="E5" t="n">
-        <v>5811.008847314267</v>
+        <v>4911.496665397945</v>
       </c>
       <c r="F5" t="n">
-        <v>5721.385431421038</v>
+        <v>4987.091961642489</v>
       </c>
       <c r="G5" t="n">
         <v>1214345</v>
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6544.393529997739</v>
+        <v>6038.393314087201</v>
       </c>
       <c r="D6" t="n">
-        <v>4237.505181626087</v>
+        <v>4226.140667004545</v>
       </c>
       <c r="E6" t="n">
-        <v>5735.381717538879</v>
+        <v>5427.535487189127</v>
       </c>
       <c r="F6" t="n">
-        <v>5706.17731486861</v>
+        <v>5308.526876185909</v>
       </c>
       <c r="G6" t="n">
         <v>943060</v>
@@ -612,16 +612,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5991.233202686336</v>
+        <v>5049.405450169224</v>
       </c>
       <c r="D7" t="n">
-        <v>3000.201665914263</v>
+        <v>2927.41148799308</v>
       </c>
       <c r="E7" t="n">
-        <v>4039.675989229487</v>
+        <v>3643.317897618024</v>
       </c>
       <c r="F7" t="n">
-        <v>4417.867329590699</v>
+        <v>3928.364842263416</v>
       </c>
       <c r="G7" t="n">
         <v>1895525</v>
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4854.986454913957</v>
+        <v>4636.536377987034</v>
       </c>
       <c r="D8" t="n">
-        <v>3334.619606783634</v>
+        <v>3537.607176466083</v>
       </c>
       <c r="E8" t="n">
-        <v>3815.326299624254</v>
+        <v>3832.388957812942</v>
       </c>
       <c r="F8" t="n">
-        <v>4033.051000660745</v>
+        <v>4039.952241365967</v>
       </c>
       <c r="G8" t="n">
         <v>3973910</v>
@@ -666,16 +666,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4579.438194532134</v>
+        <v>4768.246960130776</v>
       </c>
       <c r="D9" t="n">
-        <v>3630.09418701205</v>
+        <v>3994.548276334268</v>
       </c>
       <c r="E9" t="n">
-        <v>4116.620398576352</v>
+        <v>4526.057543949057</v>
       </c>
       <c r="F9" t="n">
-        <v>4131.896411069427</v>
+        <v>4426.183979714348</v>
       </c>
       <c r="G9" t="n">
         <v>282160</v>
@@ -693,16 +693,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3860.128216891741</v>
+        <v>3985.362503925388</v>
       </c>
       <c r="D10" t="n">
-        <v>2396.895055655953</v>
+        <v>2605.059751634401</v>
       </c>
       <c r="E10" t="n">
-        <v>2755.057301259241</v>
+        <v>2943.381864269975</v>
       </c>
       <c r="F10" t="n">
-        <v>3001.924983852329</v>
+        <v>3195.542459471982</v>
       </c>
       <c r="G10" t="n">
         <v>1283580</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4977.488790525601</v>
+        <v>4924.695472320581</v>
       </c>
       <c r="D11" t="n">
-        <v>3675.464159007716</v>
+        <v>3903.14493120889</v>
       </c>
       <c r="E11" t="n">
-        <v>4070.979075459233</v>
+        <v>4138.352970378111</v>
       </c>
       <c r="F11" t="n">
-        <v>4287.24346004364</v>
+        <v>4366.339374281933</v>
       </c>
       <c r="G11" t="n">
         <v>3286410</v>
@@ -747,16 +747,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5448.115574969082</v>
+        <v>5744.608279485228</v>
       </c>
       <c r="D12" t="n">
-        <v>4350.128307305845</v>
+        <v>4696.09600339888</v>
       </c>
       <c r="E12" t="n">
-        <v>4794.614216689673</v>
+        <v>5162.943541133692</v>
       </c>
       <c r="F12" t="n">
-        <v>4868.053180336389</v>
+        <v>5170.132231051895</v>
       </c>
       <c r="G12" t="n">
         <v>159455</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4254.760218060303</v>
+        <v>4429.72027559567</v>
       </c>
       <c r="D13" t="n">
-        <v>2719.682303042932</v>
+        <v>2920.59986030208</v>
       </c>
       <c r="E13" t="n">
-        <v>3135.222149768143</v>
+        <v>3322.224530919725</v>
       </c>
       <c r="F13" t="n">
-        <v>3371.70624106163</v>
+        <v>3577.128540379784</v>
       </c>
       <c r="G13" t="n">
         <v>653305</v>

--- a/data_input/typology_class_combo_emissions.xlsx
+++ b/data_input/typology_class_combo_emissions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>tenure_lab</t>
+          <t>inc_lab</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -473,23 +473,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5581.095721343929</v>
+        <v>5111.51919848587</v>
       </c>
       <c r="D2" t="n">
-        <v>4694.689418447797</v>
+        <v>3940.657793975894</v>
       </c>
       <c r="E2" t="n">
-        <v>4825.426378082513</v>
+        <v>4435.780155409547</v>
       </c>
       <c r="F2" t="n">
-        <v>5055.878985103967</v>
+        <v>4544.902489885828</v>
       </c>
       <c r="G2" t="n">
-        <v>2435385</v>
+        <v>1308040</v>
       </c>
     </row>
     <row r="3">
@@ -500,23 +500,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>private rental</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9016.349284731297</v>
+        <v>6014.747791854893</v>
       </c>
       <c r="D3" t="n">
-        <v>6958.997753521457</v>
+        <v>4884.409403338443</v>
       </c>
       <c r="E3" t="n">
-        <v>7091.124522305787</v>
+        <v>5208.557583589993</v>
       </c>
       <c r="F3" t="n">
-        <v>7646.991750279551</v>
+        <v>5389.959116713238</v>
       </c>
       <c r="G3" t="n">
-        <v>107480</v>
+        <v>543240</v>
       </c>
     </row>
     <row r="4">
@@ -527,50 +527,50 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>poorest 50%</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6169.284248133609</v>
+        <v>5212.468664148926</v>
       </c>
       <c r="D4" t="n">
-        <v>4733.062415568348</v>
+        <v>3927.744151723606</v>
       </c>
       <c r="E4" t="n">
-        <v>5589.101621420755</v>
+        <v>4310.389520408152</v>
       </c>
       <c r="F4" t="n">
-        <v>5556.859111992361</v>
+        <v>4467.731160281024</v>
       </c>
       <c r="G4" t="n">
-        <v>5240</v>
+        <v>607300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>detached</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>top 1%</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5740.136885743651</v>
+        <v>9306.47532605302</v>
       </c>
       <c r="D5" t="n">
-        <v>4121.144441110479</v>
+        <v>5962.187195453771</v>
       </c>
       <c r="E5" t="n">
-        <v>4911.496665397945</v>
+        <v>6720.365585093559</v>
       </c>
       <c r="F5" t="n">
-        <v>4987.091961642489</v>
+        <v>7254.833467960535</v>
       </c>
       <c r="G5" t="n">
-        <v>1214345</v>
+        <v>90465</v>
       </c>
     </row>
     <row r="6">
@@ -581,23 +581,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>private rental</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6038.393314087201</v>
+        <v>5467.86178759557</v>
       </c>
       <c r="D6" t="n">
-        <v>4226.140667004545</v>
+        <v>3451.216097061667</v>
       </c>
       <c r="E6" t="n">
-        <v>5427.535487189127</v>
+        <v>4453.144266790459</v>
       </c>
       <c r="F6" t="n">
-        <v>5308.526876185909</v>
+        <v>4490.148996766725</v>
       </c>
       <c r="G6" t="n">
-        <v>943060</v>
+        <v>1203210</v>
       </c>
     </row>
     <row r="7">
@@ -608,77 +608,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5049.405450169224</v>
+        <v>6000.931866518476</v>
       </c>
       <c r="D7" t="n">
-        <v>2927.41148799308</v>
+        <v>4201.494296522991</v>
       </c>
       <c r="E7" t="n">
-        <v>3643.317897618024</v>
+        <v>5329.527485225737</v>
       </c>
       <c r="F7" t="n">
-        <v>3928.364842263416</v>
+        <v>5279.367689045821</v>
       </c>
       <c r="G7" t="n">
-        <v>1895525</v>
+        <v>257735</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>row house</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>poorest 50%</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4636.536377987034</v>
+        <v>4965.361423184101</v>
       </c>
       <c r="D8" t="n">
-        <v>3537.607176466083</v>
+        <v>2845.023935659352</v>
       </c>
       <c r="E8" t="n">
-        <v>3832.388957812942</v>
+        <v>3739.493752035256</v>
       </c>
       <c r="F8" t="n">
-        <v>4039.952241365967</v>
+        <v>3857.941751041549</v>
       </c>
       <c r="G8" t="n">
-        <v>3973910</v>
+        <v>2566755</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>row house</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>private rental</t>
+          <t>top 1%</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4768.246960130776</v>
+        <v>8838.663633345648</v>
       </c>
       <c r="D9" t="n">
-        <v>3994.548276334268</v>
+        <v>5717.580834325356</v>
       </c>
       <c r="E9" t="n">
-        <v>4526.057543949057</v>
+        <v>6511.104831709066</v>
       </c>
       <c r="F9" t="n">
-        <v>4426.183979714348</v>
+        <v>6711.948561837584</v>
       </c>
       <c r="G9" t="n">
-        <v>282160</v>
+        <v>29710</v>
       </c>
     </row>
     <row r="10">
@@ -689,104 +689,212 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3985.362503925388</v>
+        <v>4486.194038712213</v>
       </c>
       <c r="D10" t="n">
-        <v>2605.059751634401</v>
+        <v>3028.003469168721</v>
       </c>
       <c r="E10" t="n">
-        <v>2943.381864269975</v>
+        <v>3646.431619576658</v>
       </c>
       <c r="F10" t="n">
-        <v>3195.542459471982</v>
+        <v>3798.650542815845</v>
       </c>
       <c r="G10" t="n">
-        <v>1283580</v>
+        <v>2676820</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>semi-detached</t>
+          <t>row house</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4924.695472320581</v>
+        <v>5466.760807091032</v>
       </c>
       <c r="D11" t="n">
-        <v>3903.14493120889</v>
+        <v>3821.926375146114</v>
       </c>
       <c r="E11" t="n">
-        <v>4138.352970378111</v>
+        <v>4613.654804490987</v>
       </c>
       <c r="F11" t="n">
-        <v>4366.339374281933</v>
+        <v>4678.440862002436</v>
       </c>
       <c r="G11" t="n">
-        <v>3286410</v>
+        <v>490575</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>semi-detached</t>
+          <t>row house</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>private rental</t>
+          <t>poorest 50%</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5744.608279485228</v>
+        <v>4024.679710318929</v>
       </c>
       <c r="D12" t="n">
-        <v>4696.09600339888</v>
+        <v>2596.928732785874</v>
       </c>
       <c r="E12" t="n">
-        <v>5162.943541133692</v>
+        <v>3030.934174804303</v>
       </c>
       <c r="F12" t="n">
-        <v>5170.132231051895</v>
+        <v>3185.063698749923</v>
       </c>
       <c r="G12" t="n">
-        <v>159455</v>
+        <v>2342555</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>top 1%</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8145.191972325329</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5061.975387101282</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5640.888183672378</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6205.750451363652</v>
+      </c>
+      <c r="G13" t="n">
+        <v>31110</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>semi-detached</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>social rental</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>4429.72027559567</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2920.59986030208</v>
-      </c>
-      <c r="E13" t="n">
-        <v>3322.224530919725</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3577.128540379784</v>
-      </c>
-      <c r="G13" t="n">
-        <v>653305</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>51-90%</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4661.522411221639</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3338.030891300687</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3867.856009399367</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4035.267927314456</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2078210</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>91-99%</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5644.570818443017</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4202.452977659183</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4824.387702756295</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4944.43158717526</v>
+      </c>
+      <c r="G15" t="n">
+        <v>460835</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>poorest 50%</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4454.719178275891</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2945.592637115525</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3455.081420092031</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3594.736860514034</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1523480</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>semi-detached</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>top 1%</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8252.372023344085</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5116.29942598844</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5992.720662633797</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6553.299868893439</v>
+      </c>
+      <c r="G17" t="n">
+        <v>37550</v>
       </c>
     </row>
   </sheetData>
